--- a/StructureDefinition-SEEHDSLMReferralOutcomeV31.xlsx
+++ b/StructureDefinition-SEEHDSLMReferralOutcomeV31.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T12:51:47+00:00</t>
+    <t>2026-10-12T13:38:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMReferralOutcomeV31.xlsx
+++ b/StructureDefinition-SEEHDSLMReferralOutcomeV31.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4120" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4120" uniqueCount="353">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T13:38:08+00:00</t>
+    <t>2026-10-15T17:10:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -817,6 +817,10 @@
   </si>
   <si>
     <t>Resultat av åtgärd. Data i form av bifogade bilder eller liknande.</t>
+  </si>
+  <si>
+    <t>getreferraloutcome-actresult-choice:Ett och endast ett av value och reference ska anges {value.exists() xor reference.exists()}
+ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
   </si>
   <si>
     <t>SEEHDSLMReferralOutcomeV31.referralOutcome.referralOutcomeBody.act.actResult.id</t>
@@ -9402,15 +9406,15 @@
         <v>72</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>81</v>
+        <v>261</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9507,10 +9511,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9609,10 +9613,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9713,10 +9717,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -9796,7 +9800,7 @@
         <v>72</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>73</v>
@@ -9813,10 +9817,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -9842,10 +9846,10 @@
         <v>112</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -9896,7 +9900,7 @@
         <v>72</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>83</v>
@@ -9913,10 +9917,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -9939,13 +9943,13 @@
         <v>72</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -9996,7 +10000,7 @@
         <v>72</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>73</v>
@@ -10013,10 +10017,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10039,13 +10043,13 @@
         <v>72</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -10096,7 +10100,7 @@
         <v>72</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>73</v>
@@ -10113,10 +10117,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10142,10 +10146,10 @@
         <v>78</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -10196,7 +10200,7 @@
         <v>72</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>83</v>
@@ -10213,10 +10217,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10313,10 +10317,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10415,10 +10419,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10519,10 +10523,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10548,10 +10552,10 @@
         <v>112</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -10602,7 +10606,7 @@
         <v>72</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>83</v>
@@ -10619,10 +10623,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10648,10 +10652,10 @@
         <v>112</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -10702,7 +10706,7 @@
         <v>72</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>83</v>
@@ -10719,10 +10723,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -10748,10 +10752,10 @@
         <v>122</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -10802,7 +10806,7 @@
         <v>72</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>73</v>
@@ -10819,10 +10823,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -10848,10 +10852,10 @@
         <v>78</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -10902,7 +10906,7 @@
         <v>72</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>83</v>
@@ -10919,10 +10923,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11019,10 +11023,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11121,10 +11125,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11225,10 +11229,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11254,10 +11258,10 @@
         <v>122</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -11308,7 +11312,7 @@
         <v>72</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>83</v>
@@ -11325,10 +11329,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11354,10 +11358,10 @@
         <v>112</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -11408,7 +11412,7 @@
         <v>72</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>73</v>
@@ -11425,10 +11429,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -11508,7 +11512,7 @@
         <v>72</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>73</v>
@@ -11525,10 +11529,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -11557,7 +11561,7 @@
         <v>146</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -11608,7 +11612,7 @@
         <v>72</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>73</v>
@@ -11625,10 +11629,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -11708,7 +11712,7 @@
         <v>72</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>73</v>
@@ -11725,10 +11729,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -11825,10 +11829,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -11927,10 +11931,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12031,10 +12035,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12114,7 +12118,7 @@
         <v>72</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>73</v>
@@ -12131,10 +12135,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12214,7 +12218,7 @@
         <v>72</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>73</v>
@@ -12231,10 +12235,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12314,7 +12318,7 @@
         <v>72</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>73</v>
@@ -12331,10 +12335,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -12414,7 +12418,7 @@
         <v>72</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>73</v>
@@ -12431,10 +12435,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -12514,7 +12518,7 @@
         <v>72</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>73</v>
@@ -12531,10 +12535,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -12614,7 +12618,7 @@
         <v>72</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>73</v>
@@ -12631,10 +12635,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -12714,7 +12718,7 @@
         <v>72</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>73</v>
@@ -12731,10 +12735,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -12814,7 +12818,7 @@
         <v>72</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>73</v>
@@ -12831,10 +12835,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -12860,10 +12864,10 @@
         <v>112</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -12914,7 +12918,7 @@
         <v>72</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>73</v>
@@ -12931,10 +12935,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -12960,10 +12964,10 @@
         <v>78</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -13014,7 +13018,7 @@
         <v>72</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>73</v>
@@ -13031,10 +13035,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -13131,10 +13135,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -13233,10 +13237,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -13337,10 +13341,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -13366,7 +13370,7 @@
         <v>122</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M119" t="s" s="2">
         <v>184</v>
@@ -13420,7 +13424,7 @@
         <v>72</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>83</v>
@@ -13437,10 +13441,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -13466,10 +13470,10 @@
         <v>112</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -13520,7 +13524,7 @@
         <v>72</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>73</v>
@@ -13537,10 +13541,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -13566,10 +13570,10 @@
         <v>112</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -13620,7 +13624,7 @@
         <v>72</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>73</v>
@@ -13637,10 +13641,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -13666,10 +13670,10 @@
         <v>78</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -13720,7 +13724,7 @@
         <v>72</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>83</v>
@@ -13737,10 +13741,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -13837,10 +13841,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -13939,10 +13943,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -14043,10 +14047,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -14072,10 +14076,10 @@
         <v>112</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -14126,7 +14130,7 @@
         <v>72</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>83</v>
@@ -14143,10 +14147,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -14172,10 +14176,10 @@
         <v>112</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -14226,7 +14230,7 @@
         <v>72</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>73</v>
@@ -14243,10 +14247,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -14272,10 +14276,10 @@
         <v>112</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -14326,7 +14330,7 @@
         <v>72</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>83</v>
@@ -14343,10 +14347,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -14372,10 +14376,10 @@
         <v>112</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -14426,7 +14430,7 @@
         <v>72</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>73</v>
@@ -14443,10 +14447,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -14472,10 +14476,10 @@
         <v>112</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -14526,7 +14530,7 @@
         <v>72</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>73</v>

--- a/StructureDefinition-SEEHDSLMReferralOutcomeV31.xlsx
+++ b/StructureDefinition-SEEHDSLMReferralOutcomeV31.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T17:10:15+00:00</t>
+    <t>2026-10-15T18:03:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMReferralOutcomeV31.xlsx
+++ b/StructureDefinition-SEEHDSLMReferralOutcomeV31.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T18:03:33+00:00</t>
+    <t>2026-10-26T15:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
